--- a/diseases/d227/2026-2029.xlsx
+++ b/diseases/d227/2026-2029.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7022,7 +7022,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7820,7 +7820,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8222,7 +8222,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9026,7 +9026,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9422,7 +9422,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9824,7 +9824,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11432,7 +11432,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11584,16 +11584,16 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>5100</v>
+        <v>5095</v>
       </c>
       <c r="O56" t="n">
-        <v>5100</v>
+        <v>5095</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>9.883646611339435</v>
+        <v>9.873956761720473</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -11746,10 +11746,10 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>5100</v>
+        <v>5095</v>
       </c>
       <c r="O57" t="n">
-        <v>5100</v>
+        <v>5095</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12230,7 +12230,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12632,7 +12632,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13436,7 +13436,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13588,16 +13588,16 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>5538</v>
+        <v>5545</v>
       </c>
       <c r="O66" t="n">
-        <v>5538</v>
+        <v>5545</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>10.73247743796035</v>
+        <v>10.74604322742689</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -13750,10 +13750,10 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>5538</v>
+        <v>5545</v>
       </c>
       <c r="O67" t="n">
-        <v>5538</v>
+        <v>5545</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14234,7 +14234,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14636,7 +14636,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15038,7 +15038,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15440,7 +15440,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15592,16 +15592,16 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>1125</v>
+        <v>1438</v>
       </c>
       <c r="O76" t="n">
-        <v>1125</v>
+        <v>1438</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>2.180216164266052</v>
+        <v>2.786800750412962</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -15754,10 +15754,10 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>1125</v>
+        <v>1438</v>
       </c>
       <c r="O77" t="n">
-        <v>1125</v>
+        <v>1438</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -15836,7 +15836,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16099,7 +16099,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>33227</v>
+        <v>33542</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d227/2026-2029.xlsx
+++ b/diseases/d227/2026-2029.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7022,7 +7022,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7820,7 +7820,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8222,7 +8222,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9026,7 +9026,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9422,7 +9422,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9824,7 +9824,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11432,7 +11432,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11584,16 +11584,16 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>5095</v>
+        <v>5090</v>
       </c>
       <c r="O56" t="n">
-        <v>5095</v>
+        <v>5090</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>9.873956761720473</v>
+        <v>9.864266912101515</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -11746,10 +11746,10 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>5095</v>
+        <v>5090</v>
       </c>
       <c r="O57" t="n">
-        <v>5095</v>
+        <v>5090</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12230,7 +12230,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12632,7 +12632,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13436,7 +13436,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13588,16 +13588,16 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>5545</v>
+        <v>5554</v>
       </c>
       <c r="O66" t="n">
-        <v>5545</v>
+        <v>5554</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>10.74604322742689</v>
+        <v>10.76348495674102</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -13750,10 +13750,10 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>5545</v>
+        <v>5554</v>
       </c>
       <c r="O67" t="n">
-        <v>5545</v>
+        <v>5554</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14234,7 +14234,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14636,7 +14636,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15038,7 +15038,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15440,7 +15440,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15592,16 +15592,16 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>1438</v>
+        <v>1827</v>
       </c>
       <c r="O76" t="n">
-        <v>1438</v>
+        <v>1827</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>2.786800750412962</v>
+        <v>3.540671050768068</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -15754,10 +15754,10 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>1438</v>
+        <v>1827</v>
       </c>
       <c r="O77" t="n">
-        <v>1438</v>
+        <v>1827</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -15836,7 +15836,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16099,7 +16099,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>33542</v>
+        <v>33935</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d227/2026-2029.xlsx
+++ b/diseases/d227/2026-2029.xlsx
@@ -11584,16 +11584,16 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>5090</v>
+        <v>5089</v>
       </c>
       <c r="O56" t="n">
-        <v>5090</v>
+        <v>5089</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>9.864266912101515</v>
+        <v>9.862328942177722</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -11746,10 +11746,10 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>5090</v>
+        <v>5089</v>
       </c>
       <c r="O57" t="n">
-        <v>5090</v>
+        <v>5089</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
@@ -13588,16 +13588,16 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>5554</v>
+        <v>5553</v>
       </c>
       <c r="O66" t="n">
-        <v>5554</v>
+        <v>5553</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>10.76348495674102</v>
+        <v>10.76154698681723</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -13750,10 +13750,10 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>5554</v>
+        <v>5553</v>
       </c>
       <c r="O67" t="n">
-        <v>5554</v>
+        <v>5553</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -15592,16 +15592,16 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>1827</v>
+        <v>1976</v>
       </c>
       <c r="O76" t="n">
-        <v>1827</v>
+        <v>1976</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>3.540671050768068</v>
+        <v>3.829428569413083</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -15754,10 +15754,10 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>1827</v>
+        <v>1976</v>
       </c>
       <c r="O77" t="n">
-        <v>1827</v>
+        <v>1976</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -15918,6 +15918,408 @@
       <c r="BC77" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>carbapenem-resistant-enterobacterales-infection</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>碳青霉烯耐药肠杆菌目细菌感染</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>14</v>
+      </c>
+      <c r="O78" t="n">
+        <v>14</v>
+      </c>
+      <c r="P78" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0.01143531770592073</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>SER_JP_CRE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP78" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ78" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr">
+        <is>
+          <t>SER_JP_CRE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV78" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA78" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB78" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC78" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>carbapenem-resistant-enterobacterales-infection</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>碳青霉烯耐药肠杆菌目细菌感染</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>14</v>
+      </c>
+      <c r="O79" t="n">
+        <v>14</v>
+      </c>
+      <c r="P79" t="n">
+        <v>14</v>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>SER_JP_CRE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>SER_JP_CRE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Japan NIID carbapenem-resistant Enterobacterales infection notifications.</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN79" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP79" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ79" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr">
+        <is>
+          <t>SER_JP_CRE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV79" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA79" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB79" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC79" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -15954,7 +16356,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -16037,7 +16439,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10">
@@ -16047,7 +16449,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11">
@@ -16067,7 +16469,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">
@@ -16099,7 +16501,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>33935</v>
+        <v>34096</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d227/2026-2029.xlsx
+++ b/diseases/d227/2026-2029.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>4786</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>9.275124055268732</v>
       </c>
@@ -1014,7 +1011,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1164,9 +1161,6 @@
       <c r="P4" t="n">
         <v>9</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.007351275668091897</v>
       </c>
@@ -1416,7 +1410,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1818,7 +1812,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2220,7 +2214,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2622,7 +2616,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3024,7 +3018,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3171,9 +3165,6 @@
       <c r="O14" t="n">
         <v>3616</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>7.007699244432038</v>
       </c>
@@ -3420,7 +3411,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3822,7 +3813,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4224,7 +4215,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4626,7 +4617,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -5028,7 +5019,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5175,9 +5166,6 @@
       <c r="O24" t="n">
         <v>4159</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>8.060016913051118</v>
       </c>
@@ -5424,7 +5412,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -5826,7 +5814,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6228,7 +6216,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6630,7 +6618,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7032,7 +7020,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7179,9 +7167,6 @@
       <c r="O34" t="n">
         <v>4269</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>8.273193604668243</v>
       </c>
@@ -7428,7 +7413,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7830,7 +7815,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8232,7 +8217,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8634,7 +8619,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -9036,7 +9021,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9183,9 +9168,6 @@
       <c r="O44" t="n">
         <v>4215</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>8.168543228783474</v>
       </c>
@@ -9432,7 +9414,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9834,7 +9816,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10236,7 +10218,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10638,7 +10620,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11040,7 +11022,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11442,7 +11424,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11589,9 +11571,6 @@
       <c r="O56" t="n">
         <v>5089</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>9.862328942177722</v>
       </c>
@@ -11838,7 +11817,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -11988,9 +11967,6 @@
       <c r="P58" t="n">
         <v>16</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.01306893452105226</v>
       </c>
@@ -12240,7 +12216,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12390,9 +12366,6 @@
       <c r="P60" t="n">
         <v>13</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.01061850929835496</v>
       </c>
@@ -12642,7 +12615,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -12792,9 +12765,6 @@
       <c r="P62" t="n">
         <v>16</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.01306893452105226</v>
       </c>
@@ -13044,7 +13014,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13194,9 +13164,6 @@
       <c r="P64" t="n">
         <v>17</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0.01388574292861803</v>
       </c>
@@ -13446,7 +13413,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13588,16 +13555,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>5553</v>
+        <v>5552</v>
       </c>
       <c r="O66" t="n">
-        <v>5553</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>0</v>
+        <v>5552</v>
       </c>
       <c r="R66" t="n">
-        <v>10.76154698681723</v>
+        <v>10.75960901689344</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -13750,10 +13714,10 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>5553</v>
+        <v>5552</v>
       </c>
       <c r="O67" t="n">
-        <v>5553</v>
+        <v>5552</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -13842,7 +13806,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -13992,9 +13956,6 @@
       <c r="P68" t="n">
         <v>17</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.01388574292861803</v>
       </c>
@@ -14244,7 +14205,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14394,9 +14355,6 @@
       <c r="P70" t="n">
         <v>15</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.01225212611348649</v>
       </c>
@@ -14646,7 +14604,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -14796,9 +14754,6 @@
       <c r="P72" t="n">
         <v>15</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.01225212611348649</v>
       </c>
@@ -15048,7 +15003,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15198,9 +15153,6 @@
       <c r="P74" t="n">
         <v>11</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.00898489248322343</v>
       </c>
@@ -15450,7 +15402,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -15592,16 +15544,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>1976</v>
+        <v>2159</v>
       </c>
       <c r="O76" t="n">
-        <v>1976</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>0</v>
+        <v>2159</v>
       </c>
       <c r="R76" t="n">
-        <v>3.829428569413083</v>
+        <v>4.184077065467028</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -15754,10 +15703,10 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>1976</v>
+        <v>2159</v>
       </c>
       <c r="O77" t="n">
-        <v>1976</v>
+        <v>2159</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -15846,7 +15795,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -15996,9 +15945,6 @@
       <c r="P78" t="n">
         <v>14</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.01143531770592073</v>
       </c>
@@ -16248,7 +16194,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16501,7 +16447,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>34096</v>
+        <v>34278</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d227/2026-2029.xlsx
+++ b/diseases/d227/2026-2029.xlsx
@@ -11566,13 +11566,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>5089</v>
+        <v>5087</v>
       </c>
       <c r="O56" t="n">
-        <v>5089</v>
+        <v>5087</v>
       </c>
       <c r="R56" t="n">
-        <v>9.862328942177722</v>
+        <v>9.858453002330137</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -11725,10 +11725,10 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>5089</v>
+        <v>5087</v>
       </c>
       <c r="O57" t="n">
-        <v>5089</v>
+        <v>5087</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
@@ -13555,13 +13555,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>5552</v>
+        <v>5550</v>
       </c>
       <c r="O66" t="n">
-        <v>5552</v>
+        <v>5550</v>
       </c>
       <c r="R66" t="n">
-        <v>10.75960901689344</v>
+        <v>10.75573307704586</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -13714,10 +13714,10 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>5552</v>
+        <v>5550</v>
       </c>
       <c r="O67" t="n">
-        <v>5552</v>
+        <v>5550</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -15544,13 +15544,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>2159</v>
+        <v>2341</v>
       </c>
       <c r="O76" t="n">
-        <v>2159</v>
+        <v>2341</v>
       </c>
       <c r="R76" t="n">
-        <v>4.184077065467028</v>
+        <v>4.53678759159718</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -15703,10 +15703,10 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>2159</v>
+        <v>2341</v>
       </c>
       <c r="O77" t="n">
-        <v>2159</v>
+        <v>2341</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -16447,7 +16447,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>34278</v>
+        <v>34456</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d227/2026-2029.xlsx
+++ b/diseases/d227/2026-2029.xlsx
@@ -11566,13 +11566,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>5087</v>
+        <v>5082</v>
       </c>
       <c r="O56" t="n">
-        <v>5087</v>
+        <v>5082</v>
       </c>
       <c r="R56" t="n">
-        <v>9.858453002330137</v>
+        <v>9.848763152711177</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -11725,10 +11725,10 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>5087</v>
+        <v>5082</v>
       </c>
       <c r="O57" t="n">
-        <v>5087</v>
+        <v>5082</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
@@ -13555,13 +13555,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>5550</v>
+        <v>5544</v>
       </c>
       <c r="O66" t="n">
-        <v>5550</v>
+        <v>5544</v>
       </c>
       <c r="R66" t="n">
-        <v>10.75573307704586</v>
+        <v>10.7441052575031</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -13714,10 +13714,10 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>5550</v>
+        <v>5544</v>
       </c>
       <c r="O67" t="n">
-        <v>5550</v>
+        <v>5544</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -15544,13 +15544,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>2341</v>
+        <v>2729</v>
       </c>
       <c r="O76" t="n">
-        <v>2341</v>
+        <v>2729</v>
       </c>
       <c r="R76" t="n">
-        <v>4.53678759159718</v>
+        <v>5.288719922028493</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -15703,10 +15703,10 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>2341</v>
+        <v>2729</v>
       </c>
       <c r="O77" t="n">
-        <v>2341</v>
+        <v>2729</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -16264,6 +16264,405 @@
         </is>
       </c>
       <c r="BC79" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>carbapenem-resistant-enterobacterales-infection</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>碳青霉烯耐药肠杆菌目细菌感染</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>14</v>
+      </c>
+      <c r="O80" t="n">
+        <v>14</v>
+      </c>
+      <c r="P80" t="n">
+        <v>14</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0.01143531770592073</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>SER_JP_CRE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP80" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ80" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr">
+        <is>
+          <t>SER_JP_CRE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV80" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA80" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB80" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC80" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>carbapenem-resistant-enterobacterales-infection</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>碳青霉烯耐药肠杆菌目细菌感染</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>14</v>
+      </c>
+      <c r="O81" t="n">
+        <v>14</v>
+      </c>
+      <c r="P81" t="n">
+        <v>14</v>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>SER_JP_CRE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>SER_JP_CRE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Japan NIID carbapenem-resistant Enterobacterales infection notifications.</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN81" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP81" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ81" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr">
+        <is>
+          <t>SER_JP_CRE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV81" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA81" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB81" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC81" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -16302,7 +16701,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -16385,7 +16784,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10">
@@ -16395,7 +16794,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11">
@@ -16415,7 +16814,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
@@ -16447,7 +16846,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>34456</v>
+        <v>34847</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d227/2026-2029.xlsx
+++ b/diseases/d227/2026-2029.xlsx
@@ -11566,13 +11566,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>5082</v>
+        <v>5078</v>
       </c>
       <c r="O56" t="n">
-        <v>5082</v>
+        <v>5078</v>
       </c>
       <c r="R56" t="n">
-        <v>9.848763152711177</v>
+        <v>9.841011273016008</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -11725,10 +11725,10 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>5082</v>
+        <v>5078</v>
       </c>
       <c r="O57" t="n">
-        <v>5082</v>
+        <v>5078</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
@@ -13555,13 +13555,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>5544</v>
+        <v>5538</v>
       </c>
       <c r="O66" t="n">
-        <v>5544</v>
+        <v>5538</v>
       </c>
       <c r="R66" t="n">
-        <v>10.7441052575031</v>
+        <v>10.73247743796035</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -13714,10 +13714,10 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>5544</v>
+        <v>5538</v>
       </c>
       <c r="O67" t="n">
-        <v>5544</v>
+        <v>5538</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -15544,13 +15544,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>2729</v>
+        <v>4426</v>
       </c>
       <c r="O76" t="n">
-        <v>2729</v>
+        <v>4426</v>
       </c>
       <c r="R76" t="n">
-        <v>5.288719922028493</v>
+        <v>8.577454882703595</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -15703,10 +15703,10 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>2729</v>
+        <v>4426</v>
       </c>
       <c r="O77" t="n">
-        <v>2729</v>
+        <v>4426</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -16663,6 +16663,405 @@
         </is>
       </c>
       <c r="BC81" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>carbapenem-resistant-enterobacterales-infection</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>碳青霉烯耐药肠杆菌目细菌感染</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>11</v>
+      </c>
+      <c r="O82" t="n">
+        <v>11</v>
+      </c>
+      <c r="P82" t="n">
+        <v>11</v>
+      </c>
+      <c r="R82" t="n">
+        <v>0.00898489248322343</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>SER_JP_CRE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP82" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ82" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr">
+        <is>
+          <t>SER_JP_CRE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV82" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA82" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB82" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC82" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>carbapenem-resistant-enterobacterales-infection</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>碳青霉烯耐药肠杆菌目细菌感染</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>11</v>
+      </c>
+      <c r="O83" t="n">
+        <v>11</v>
+      </c>
+      <c r="P83" t="n">
+        <v>11</v>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>SER_JP_CRE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>SER_JP_CRE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD83" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE83" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF83" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG83" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Japan NIID carbapenem-resistant Enterobacterales infection notifications.</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN83" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP83" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ83" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr">
+        <is>
+          <t>SER_JP_CRE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV83" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA83" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB83" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC83" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -16701,7 +17100,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -16784,7 +17183,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10">
@@ -16794,7 +17193,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11">
@@ -16814,7 +17213,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
@@ -16846,7 +17245,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>34847</v>
+        <v>36545</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d227/2026-2029.xlsx
+++ b/diseases/d227/2026-2029.xlsx
@@ -15544,13 +15544,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>4426</v>
+        <v>4440</v>
       </c>
       <c r="O76" t="n">
-        <v>4426</v>
+        <v>4440</v>
       </c>
       <c r="R76" t="n">
-        <v>8.577454882703595</v>
+        <v>8.604586461636684</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -15703,10 +15703,10 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>4426</v>
+        <v>4440</v>
       </c>
       <c r="O77" t="n">
-        <v>4426</v>
+        <v>4440</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>36545</v>
+        <v>36559</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d227/2026-2029.xlsx
+++ b/diseases/d227/2026-2029.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7403,7 +7403,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8207,7 +8207,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8609,7 +8609,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9011,7 +9011,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9404,7 +9404,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9806,7 +9806,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10610,7 +10610,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11012,7 +11012,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11414,7 +11414,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11807,7 +11807,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12206,7 +12206,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12605,7 +12605,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13004,7 +13004,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13403,7 +13403,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13796,7 +13796,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14195,7 +14195,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15392,7 +15392,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15785,7 +15785,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16583,7 +16583,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16982,7 +16982,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">

--- a/diseases/d227/2026-2029.xlsx
+++ b/diseases/d227/2026-2029.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7403,7 +7403,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8207,7 +8207,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8609,7 +8609,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9011,7 +9011,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9404,7 +9404,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9806,7 +9806,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10610,7 +10610,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11012,7 +11012,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11414,7 +11414,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11807,7 +11807,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12206,7 +12206,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12605,7 +12605,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13004,7 +13004,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13403,7 +13403,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13796,7 +13796,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14195,7 +14195,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15392,7 +15392,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15785,7 +15785,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16583,7 +16583,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16982,7 +16982,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">

--- a/diseases/d227/2026-2029.xlsx
+++ b/diseases/d227/2026-2029.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7403,7 +7403,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8207,7 +8207,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8609,7 +8609,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9011,7 +9011,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9404,7 +9404,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9806,7 +9806,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10610,7 +10610,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11012,7 +11012,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11414,7 +11414,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11807,7 +11807,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12206,7 +12206,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12605,7 +12605,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13004,7 +13004,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13403,7 +13403,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13796,7 +13796,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14195,7 +14195,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15392,7 +15392,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15785,7 +15785,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16583,7 +16583,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16982,7 +16982,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">

--- a/diseases/d227/2026-2029.xlsx
+++ b/diseases/d227/2026-2029.xlsx
@@ -13555,13 +13555,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>5538</v>
+        <v>5536</v>
       </c>
       <c r="O66" t="n">
-        <v>5538</v>
+        <v>5536</v>
       </c>
       <c r="R66" t="n">
-        <v>10.73247743796035</v>
+        <v>10.72860149811277</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -13714,10 +13714,10 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>5538</v>
+        <v>5536</v>
       </c>
       <c r="O67" t="n">
-        <v>5538</v>
+        <v>5536</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -15544,13 +15544,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>4440</v>
+        <v>4554</v>
       </c>
       <c r="O76" t="n">
-        <v>4440</v>
+        <v>4554</v>
       </c>
       <c r="R76" t="n">
-        <v>8.604586461636684</v>
+        <v>8.825515032948976</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -15703,10 +15703,10 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>4440</v>
+        <v>4554</v>
       </c>
       <c r="O77" t="n">
-        <v>4440</v>
+        <v>4554</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>36559</v>
+        <v>36671</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d227/2026-2029.xlsx
+++ b/diseases/d227/2026-2029.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7403,7 +7403,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8207,7 +8207,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8609,7 +8609,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9011,7 +9011,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9404,7 +9404,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9806,7 +9806,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10610,7 +10610,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11012,7 +11012,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11414,7 +11414,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11807,7 +11807,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12206,7 +12206,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12605,7 +12605,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13004,7 +13004,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13403,7 +13403,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13796,7 +13796,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14195,7 +14195,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15392,7 +15392,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15785,7 +15785,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16583,7 +16583,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16982,7 +16982,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">

--- a/diseases/d227/2026-2029.xlsx
+++ b/diseases/d227/2026-2029.xlsx
@@ -13555,13 +13555,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>5536</v>
+        <v>5535</v>
       </c>
       <c r="O66" t="n">
-        <v>5536</v>
+        <v>5535</v>
       </c>
       <c r="R66" t="n">
-        <v>10.72860149811277</v>
+        <v>10.72666352818897</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -13714,10 +13714,10 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>5536</v>
+        <v>5535</v>
       </c>
       <c r="O67" t="n">
-        <v>5536</v>
+        <v>5535</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -15544,13 +15544,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>4554</v>
+        <v>5415</v>
       </c>
       <c r="O76" t="n">
-        <v>4554</v>
+        <v>5415</v>
       </c>
       <c r="R76" t="n">
-        <v>8.825515032948976</v>
+        <v>10.49410713733393</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -15703,10 +15703,10 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>4554</v>
+        <v>5415</v>
       </c>
       <c r="O77" t="n">
-        <v>4554</v>
+        <v>5415</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -17064,6 +17064,798 @@
       <c r="BC83" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>carbapenem-resistant-enterobacterales-infection</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>碳青霉烯耐药肠杆菌目细菌感染</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>19</v>
+      </c>
+      <c r="O84" t="n">
+        <v>19</v>
+      </c>
+      <c r="P84" t="n">
+        <v>19</v>
+      </c>
+      <c r="R84" t="n">
+        <v>0.01551935974374956</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>SER_JP_CRE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP84" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ84" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr">
+        <is>
+          <t>SER_JP_CRE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV84" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA84" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB84" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC84" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>carbapenem-resistant-enterobacterales-infection</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>碳青霉烯耐药肠杆菌目细菌感染</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>19</v>
+      </c>
+      <c r="O85" t="n">
+        <v>19</v>
+      </c>
+      <c r="P85" t="n">
+        <v>19</v>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>SER_JP_CRE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>SER_JP_CRE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD85" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE85" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF85" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG85" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Japan NIID carbapenem-resistant Enterobacterales infection notifications.</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN85" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP85" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ85" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr">
+        <is>
+          <t>SER_JP_CRE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV85" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA85" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB85" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC85" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>carbapenem-resistant-enterobacterales-infection</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>碳青霉烯耐药肠杆菌目细菌感染</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>346</v>
+      </c>
+      <c r="O86" t="n">
+        <v>346</v>
+      </c>
+      <c r="R86" t="n">
+        <v>0.6705375936320479</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>SER_KR_CRE</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP86" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ86" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS86" t="inlineStr">
+        <is>
+          <t>SER_KR_CRE</t>
+        </is>
+      </c>
+      <c r="AT86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV86" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA86" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB86" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC86" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>carbapenem-resistant-enterobacterales-infection</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>D227</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Carbapenem-resistant Enterobacterales infection</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>碳青霉烯耐药肠杆菌目细菌感染</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N87" t="n">
+        <v>346</v>
+      </c>
+      <c r="O87" t="n">
+        <v>346</v>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>SER_KR_CRE</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>SER_KR_CRE</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>SRC_KR_KDCA</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>카바페넴내성장내세균목(CRE) 감염증</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>country:KR:national</t>
+        </is>
+      </c>
+      <c r="AD87" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE87" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF87" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG87" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Korea KDCA carbapenem-resistant Enterobacterales infection category.</t>
+        </is>
+      </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN87" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP87" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ87" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr">
+        <is>
+          <t>SER_KR_CRE</t>
+        </is>
+      </c>
+      <c r="AT87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV87" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA87" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB87" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC87" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -17100,7 +17892,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -17183,7 +17975,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10">
@@ -17193,7 +17985,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11">
@@ -17213,7 +18005,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13">
@@ -17245,7 +18037,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>36671</v>
+        <v>37896</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d227/2026-2029.xlsx
+++ b/diseases/d227/2026-2029.xlsx
@@ -13555,13 +13555,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>5535</v>
+        <v>5530</v>
       </c>
       <c r="O66" t="n">
-        <v>5535</v>
+        <v>5530</v>
       </c>
       <c r="R66" t="n">
-        <v>10.72666352818897</v>
+        <v>10.71697367857001</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -13714,10 +13714,10 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>5535</v>
+        <v>5530</v>
       </c>
       <c r="O67" t="n">
-        <v>5535</v>
+        <v>5530</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -15544,13 +15544,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>5415</v>
+        <v>5421</v>
       </c>
       <c r="O76" t="n">
-        <v>5415</v>
+        <v>5421</v>
       </c>
       <c r="R76" t="n">
-        <v>10.49410713733393</v>
+        <v>10.50573495687668</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -15703,10 +15703,10 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>5415</v>
+        <v>5421</v>
       </c>
       <c r="O77" t="n">
-        <v>5415</v>
+        <v>5421</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -17533,13 +17533,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>346</v>
+        <v>462</v>
       </c>
       <c r="O86" t="n">
-        <v>346</v>
+        <v>462</v>
       </c>
       <c r="R86" t="n">
-        <v>0.6705375936320479</v>
+        <v>0.8953421047919251</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -17692,10 +17692,10 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>346</v>
+        <v>462</v>
       </c>
       <c r="O87" t="n">
-        <v>346</v>
+        <v>462</v>
       </c>
       <c r="U87" t="inlineStr">
         <is>
@@ -18037,7 +18037,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>37896</v>
+        <v>38013</v>
       </c>
     </row>
     <row r="16">
